--- a/data/warn-scraper/cache/mt/source.xlsx
+++ b/data/warn-scraper/cache/mt/source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mtgov-my.sharepoint.com/personal/ce0501_mt_gov/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="191" documentId="8_{9E658140-0375-4196-8AF4-54A17CD16374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2F450AB-E22B-4B66-89CA-7E5E8EEBE0FB}"/>
+  <xr:revisionPtr revIDLastSave="213" documentId="8_{9E658140-0375-4196-8AF4-54A17CD16374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{555D3B3C-FB7D-42E2-A92D-D87513070416}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9EEBCBD0-1086-4593-A928-76738C10FB2E}"/>
+    <workbookView xWindow="4410" yWindow="1995" windowWidth="21600" windowHeight="11295" xr2:uid="{9EEBCBD0-1086-4593-A928-76738C10FB2E}"/>
   </bookViews>
   <sheets>
     <sheet name="WARN" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="114">
   <si>
     <t>Date of Notice</t>
   </si>
@@ -362,6 +362,12 @@
   </si>
   <si>
     <t>Hydrocarbon exploration/Drilling</t>
+  </si>
+  <si>
+    <t>Banking</t>
+  </si>
+  <si>
+    <t>Wells Fargo &amp; Company</t>
   </si>
 </sst>
 </file>
@@ -500,7 +506,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -536,12 +542,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -593,6 +593,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -908,7 +911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D0C4581-54A0-444B-96BE-38D309589FE1}">
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
@@ -943,565 +946,555 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="26">
+      <c r="A2" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="5">
+        <v>46111</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="5">
+        <v>46172</v>
+      </c>
+      <c r="G2" s="6">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="24"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="6"/>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="24">
         <v>2025</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B4" s="5">
         <v>45743</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C4" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F4" s="5">
         <v>45436</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G4" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="26"/>
-      <c r="B3" s="5">
+    <row r="5" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="24"/>
+      <c r="B5" s="5">
         <v>45750</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E5" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G5" s="6">
         <v>164</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="26"/>
-      <c r="B4" s="5">
+    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="24"/>
+      <c r="B6" s="5">
         <v>45772</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F6" s="5">
         <v>45836</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G6" s="6">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="26"/>
-      <c r="B5" s="5">
+    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="24"/>
+      <c r="B7" s="5">
         <v>45866</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C7" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="5">
-        <v>45927</v>
-      </c>
-      <c r="G5" s="6">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="26"/>
-      <c r="B6" s="5">
-        <v>45887</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="F6" s="5">
-        <v>45955</v>
-      </c>
-      <c r="G6" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="26"/>
-      <c r="B7" s="5">
-        <v>45926</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="5">
+        <v>45927</v>
+      </c>
+      <c r="G7" s="6">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="24"/>
+      <c r="B8" s="5">
+        <v>45887</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F8" s="5">
+        <v>45955</v>
+      </c>
+      <c r="G8" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="24"/>
+      <c r="B9" s="5">
+        <v>45926</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F9" s="5">
         <v>46022</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G9" s="6">
         <v>300</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="26"/>
-      <c r="B8" s="5">
+    <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="24"/>
+      <c r="B10" s="5">
         <v>45957</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C10" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D10" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E10" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F10" s="5">
         <v>45994</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G10" s="6">
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="26"/>
-      <c r="B9" s="5">
+    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="24"/>
+      <c r="B11" s="5">
         <v>45959</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C11" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D11" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E11" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F11" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G11" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="26"/>
-      <c r="B10" s="5" t="s">
+    <row r="12" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="24"/>
+      <c r="B12" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C12" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D12" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E12" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F12" s="5">
         <v>46037</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G12" s="6">
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="26"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="26"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-    </row>
     <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="29">
+      <c r="A13" s="24"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="6"/>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="24"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
         <v>2024</v>
       </c>
-      <c r="B13" s="22">
+      <c r="B15" s="20">
         <v>45380</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C15" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D15" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="E15" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F15" s="20">
         <v>45443</v>
       </c>
-      <c r="G13" s="23">
+      <c r="G15" s="21">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="28"/>
-      <c r="B14" s="22">
+    <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="26"/>
+      <c r="B16" s="20">
         <v>45365</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C16" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D16" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="23" t="s">
+      <c r="E16" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F16" s="20">
         <v>45413</v>
       </c>
-      <c r="G14" s="32">
+      <c r="G16" s="30">
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="29"/>
-      <c r="B15" s="22">
+    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="27"/>
+      <c r="B17" s="20">
         <v>45371</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C17" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D17" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="23" t="s">
+      <c r="E17" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F17" s="20">
         <v>45434</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G17" s="21">
         <v>159</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="30"/>
-      <c r="B16" s="22">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="28"/>
+      <c r="B18" s="20">
         <v>45547</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C18" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D18" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E18" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F18" s="20">
         <v>45608</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G18" s="21">
         <v>700</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="30"/>
-      <c r="B17" s="22">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="28"/>
+      <c r="B19" s="20">
         <v>45551</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="C19" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="D17" s="33" t="s">
+      <c r="D19" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="E17" s="31" t="s">
+      <c r="E19" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F19" s="20">
         <v>45611</v>
       </c>
-      <c r="G17" s="32">
+      <c r="G19" s="30">
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="30"/>
-      <c r="B18" s="22">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="28"/>
+      <c r="B20" s="20">
         <v>45558</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C20" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="D18" s="33" t="s">
+      <c r="D20" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E20" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="F18" s="22">
+      <c r="F20" s="20">
         <v>45560</v>
       </c>
-      <c r="G18" s="32">
+      <c r="G20" s="30">
         <v>109</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="30"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="32"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="21"/>
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="27"/>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="28"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="30"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="25"/>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="23">
         <v>2023</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B23" s="9">
         <v>44963</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="C23" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D23" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="20" t="s">
+      <c r="E23" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F23" s="9">
         <v>45030</v>
       </c>
-      <c r="G21" s="20" t="s">
+      <c r="G23" s="18" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="21"/>
-      <c r="B22" s="22">
+    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="19"/>
+      <c r="B24" s="20">
         <v>45139</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C24" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="D22" s="23" t="s">
+      <c r="D24" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E24" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="22" t="s">
+      <c r="F24" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="G22" s="23">
+      <c r="G24" s="21">
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="21"/>
-      <c r="B23" s="22">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="19"/>
+      <c r="B25" s="20">
         <v>45161</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C25" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="D23" s="23" t="s">
+      <c r="D25" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="E23" s="23" t="s">
+      <c r="E25" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="F23" s="22">
+      <c r="F25" s="20">
         <v>45226</v>
       </c>
-      <c r="G23" s="23">
+      <c r="G25" s="21">
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="21"/>
-      <c r="B24" s="22">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="19"/>
+      <c r="B26" s="20">
         <v>45174</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C26" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="23" t="s">
+      <c r="D26" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="E24" s="23" t="s">
+      <c r="E26" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="F24" s="22">
+      <c r="F26" s="20">
         <v>45231</v>
       </c>
-      <c r="G24" s="23" t="s">
+      <c r="G26" s="21" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="26">
+    <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="24">
         <v>2021</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B27" s="5">
         <v>44438</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C27" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D27" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E27" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F27" s="5">
         <v>44530</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G27" s="6">
         <v>99</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="26">
+    <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="24">
         <v>2020</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B28" s="5">
         <v>43843</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C28" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D28" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E28" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F28" s="5">
         <v>43922</v>
       </c>
-      <c r="G26" s="6">
+      <c r="G28" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="13"/>
-      <c r="B27" s="5">
+    <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="6"/>
+      <c r="B29" s="5">
         <v>43871</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C29" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F27" s="5">
-        <v>43946</v>
-      </c>
-      <c r="G27" s="6">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="14"/>
-      <c r="B28" s="5">
-        <v>43914</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F28" s="5">
-        <v>43915</v>
-      </c>
-      <c r="G28" s="6">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="14"/>
-      <c r="B29" s="5">
-        <v>43915</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F29" s="5">
-        <v>43915</v>
+        <v>43946</v>
       </c>
       <c r="G29" s="6">
-        <v>85</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="15"/>
+      <c r="A30" s="6"/>
       <c r="B30" s="5">
-        <v>43915</v>
+        <v>43914</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>36</v>
@@ -1510,392 +1503,434 @@
         <v>43915</v>
       </c>
       <c r="G30" s="6">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="6"/>
+      <c r="B31" s="5">
+        <v>43915</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F31" s="5">
+        <v>43915</v>
+      </c>
+      <c r="G31" s="6">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="5">
+        <v>43915</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F32" s="5">
+        <v>43915</v>
+      </c>
+      <c r="G32" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="15"/>
-      <c r="B31" s="5">
+    <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="13"/>
+      <c r="B33" s="5">
         <v>43916</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C33" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D33" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E33" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F33" s="5">
         <v>43916</v>
       </c>
-      <c r="G31" s="6">
+      <c r="G33" s="6">
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="15"/>
-      <c r="B32" s="5">
+    <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="13"/>
+      <c r="B34" s="5">
         <v>43924</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C34" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D34" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E34" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F34" s="5">
         <v>43924</v>
       </c>
-      <c r="G32" s="6">
+      <c r="G34" s="6">
         <v>94</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="15"/>
-      <c r="B33" s="5">
+    <row r="35" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="13"/>
+      <c r="B35" s="5">
         <v>43924</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C35" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D35" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E35" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F35" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="G33" s="6">
+      <c r="G35" s="6">
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="15"/>
-      <c r="B34" s="5">
+    <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="13"/>
+      <c r="B36" s="5">
         <v>43941</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C36" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D36" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E36" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F36" s="5">
         <v>43913</v>
       </c>
-      <c r="G34" s="6">
+      <c r="G36" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="15"/>
-      <c r="B35" s="5">
+    <row r="37" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="13"/>
+      <c r="B37" s="5">
         <v>43941</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C37" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D37" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F35" s="5">
-        <v>43913</v>
-      </c>
-      <c r="G35" s="6">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="15"/>
-      <c r="B36" s="5">
-        <v>43956</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F36" s="5">
-        <v>44019</v>
-      </c>
-      <c r="G36" s="6">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="15"/>
-      <c r="B37" s="5">
-        <v>44174</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>38</v>
       </c>
       <c r="F37" s="5">
+        <v>43913</v>
+      </c>
+      <c r="G37" s="6">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="13"/>
+      <c r="B38" s="5">
+        <v>43956</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F38" s="5">
+        <v>44019</v>
+      </c>
+      <c r="G38" s="6">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="13"/>
+      <c r="B39" s="5">
+        <v>44174</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F39" s="5">
         <v>44167</v>
       </c>
-      <c r="G37" s="6">
+      <c r="G39" s="6">
         <v>76</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="15"/>
-      <c r="B38" s="5">
+    <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="13"/>
+      <c r="B40" s="5">
         <v>44174</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C40" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D40" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="E40" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F40" s="5">
         <v>44228</v>
       </c>
-      <c r="G38" s="6">
+      <c r="G40" s="6">
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="6">
+    <row r="41" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="24">
         <v>2018</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B41" s="5">
         <v>43208</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C41" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D41" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F41" s="5">
         <v>43374</v>
       </c>
-      <c r="G39" s="6">
+      <c r="G41" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
+    <row r="42" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="33">
         <v>2017</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B42" s="7">
         <v>42815</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E42" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F40" s="7">
+      <c r="F42" s="7">
         <v>42916</v>
       </c>
-      <c r="G40" s="4">
+      <c r="G42" s="4">
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+    <row r="43" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="33">
         <v>2016</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B43" s="7">
         <v>42373</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D43" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="E43" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F41" s="7">
+      <c r="F43" s="7">
         <v>42275</v>
       </c>
-      <c r="G41" s="4">
+      <c r="G43" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="16"/>
-      <c r="B42" s="7">
+    <row r="44" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="14"/>
+      <c r="B44" s="7">
         <v>42389</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C44" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D44" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="E44" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F42" s="7">
+      <c r="F44" s="7">
         <v>42460</v>
       </c>
-      <c r="G42" s="4">
+      <c r="G44" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="17"/>
-      <c r="B43" s="7">
+    <row r="45" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="15"/>
+      <c r="B45" s="7">
         <v>42459</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E45" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F43" s="7">
+      <c r="F45" s="7">
         <v>42491</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G45" s="4" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="18"/>
-      <c r="B44" s="7">
-        <v>42543</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F44" s="7">
-        <v>42617</v>
-      </c>
-      <c r="G44" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
-        <v>2015</v>
-      </c>
-      <c r="B45" s="8">
-        <v>42033</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F45" s="11">
-        <v>42094</v>
-      </c>
-      <c r="G45" s="12">
-        <v>65</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="16"/>
-      <c r="B46" s="9">
+      <c r="B46" s="7">
+        <v>42543</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F46" s="7">
+        <v>42617</v>
+      </c>
+      <c r="G46" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="33">
+        <v>2015</v>
+      </c>
+      <c r="B47" s="8">
+        <v>42033</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F47" s="11">
+        <v>42094</v>
+      </c>
+      <c r="G47" s="12">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="14"/>
+      <c r="B48" s="9">
         <v>42131</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C48" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D48" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="E48" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F46" s="11">
+      <c r="F48" s="11">
         <v>42369</v>
       </c>
-      <c r="G46" s="12">
+      <c r="G48" s="12">
         <v>341</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="17"/>
-      <c r="B47" s="9">
+    <row r="49" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="15"/>
+      <c r="B49" s="9">
         <v>42270</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C49" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D49" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E49" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F47" s="11">
+      <c r="F49" s="11">
         <v>42338</v>
       </c>
-      <c r="G47" s="12">
+      <c r="G49" s="12">
         <v>140</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="18"/>
-      <c r="B48" s="19">
+    <row r="50" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="16"/>
+      <c r="B50" s="17">
         <v>42312</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D50" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E50" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F48" s="11">
+      <c r="F50" s="11">
         <v>42355</v>
       </c>
-      <c r="G48" s="12" t="s">
+      <c r="G50" s="12" t="s">
         <v>40</v>
       </c>
     </row>

--- a/data/warn-scraper/cache/mt/source.xlsx
+++ b/data/warn-scraper/cache/mt/source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mtgov-my.sharepoint.com/personal/ce0501_mt_gov/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mtgov-my.sharepoint.com/personal/cea599_mt_gov/Documents/WebContentManagement/2026/WARN/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="213" documentId="8_{9E658140-0375-4196-8AF4-54A17CD16374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{555D3B3C-FB7D-42E2-A92D-D87513070416}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{198E6436-6B27-41BE-B620-E6262EB37063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4410" yWindow="1995" windowWidth="21600" windowHeight="11295" xr2:uid="{9EEBCBD0-1086-4593-A928-76738C10FB2E}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{9EEBCBD0-1086-4593-A928-76738C10FB2E}"/>
   </bookViews>
   <sheets>
     <sheet name="WARN" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="114">
   <si>
     <t>Date of Notice</t>
   </si>
@@ -911,7 +911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D0C4581-54A0-444B-96BE-38D309589FE1}">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
@@ -970,115 +970,91 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="24"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="5">
+        <v>46196</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F3" s="5">
+        <v>46256</v>
+      </c>
+      <c r="G3" s="6">
+        <v>16</v>
+      </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="24">
-        <v>2025</v>
-      </c>
+      <c r="A4" s="24"/>
       <c r="B4" s="5">
-        <v>45743</v>
+        <v>46224</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="F4" s="5">
-        <v>45436</v>
+        <v>46284</v>
       </c>
       <c r="G4" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="24"/>
-      <c r="B5" s="5">
-        <v>45750</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="G5" s="6">
-        <v>164</v>
-      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="6"/>
     </row>
     <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="24"/>
-      <c r="B6" s="5">
-        <v>45772</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="F6" s="5">
-        <v>45836</v>
-      </c>
-      <c r="G6" s="6">
-        <v>29</v>
-      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="6"/>
     </row>
     <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="24"/>
-      <c r="B7" s="5">
-        <v>45866</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="5">
-        <v>45927</v>
-      </c>
-      <c r="G7" s="6">
-        <v>104</v>
-      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="6"/>
     </row>
     <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="24"/>
+      <c r="A8" s="24">
+        <v>2025</v>
+      </c>
       <c r="B8" s="5">
-        <v>45887</v>
+        <v>45743</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>91</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="F8" s="5">
-        <v>45955</v>
+        <v>45436</v>
       </c>
       <c r="G8" s="6">
         <v>1</v>
@@ -1087,850 +1063,934 @@
     <row r="9" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A9" s="24"/>
       <c r="B9" s="5">
-        <v>45926</v>
+        <v>45750</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F9" s="5">
-        <v>46022</v>
+        <v>93</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="G9" s="6">
-        <v>300</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="24"/>
       <c r="B10" s="5">
-        <v>45957</v>
+        <v>45772</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F10" s="5">
-        <v>45994</v>
+        <v>45836</v>
       </c>
       <c r="G10" s="6">
-        <v>112</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="24"/>
       <c r="B11" s="5">
-        <v>45959</v>
+        <v>45866</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>106</v>
+        <v>18</v>
+      </c>
+      <c r="F11" s="5">
+        <v>45927</v>
       </c>
       <c r="G11" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="24"/>
-      <c r="B12" s="5" t="s">
-        <v>108</v>
+      <c r="B12" s="5">
+        <v>45887</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="F12" s="5">
-        <v>46037</v>
+        <v>45955</v>
       </c>
       <c r="G12" s="6">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A13" s="24"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="6"/>
+      <c r="B13" s="5">
+        <v>45926</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F13" s="5">
+        <v>46022</v>
+      </c>
+      <c r="G13" s="6">
+        <v>300</v>
+      </c>
     </row>
     <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="24"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
+      <c r="B14" s="5">
+        <v>45957</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F14" s="5">
+        <v>45994</v>
+      </c>
+      <c r="G14" s="6">
+        <v>112</v>
+      </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="27">
+      <c r="A15" s="24"/>
+      <c r="B15" s="5">
+        <v>45959</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G15" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="24"/>
+      <c r="B16" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16" s="5">
+        <v>46037</v>
+      </c>
+      <c r="G16" s="6">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="24"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="24"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
         <v>2024</v>
       </c>
-      <c r="B15" s="20">
+      <c r="B19" s="20">
         <v>45380</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C19" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D19" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E19" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F19" s="20">
         <v>45443</v>
       </c>
-      <c r="G15" s="21">
+      <c r="G19" s="21">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="26"/>
-      <c r="B16" s="20">
+    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="26"/>
+      <c r="B20" s="20">
         <v>45365</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C20" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D20" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="21" t="s">
+      <c r="E20" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F20" s="20">
         <v>45413</v>
       </c>
-      <c r="G16" s="30">
+      <c r="G20" s="30">
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="27"/>
-      <c r="B17" s="20">
+    <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="27"/>
+      <c r="B21" s="20">
         <v>45371</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C21" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="21" t="s">
+      <c r="D21" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="21" t="s">
+      <c r="E21" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F21" s="20">
         <v>45434</v>
       </c>
-      <c r="G17" s="21">
+      <c r="G21" s="21">
         <v>159</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="28"/>
-      <c r="B18" s="20">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="28"/>
+      <c r="B22" s="20">
         <v>45547</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C22" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D22" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="E18" s="29" t="s">
+      <c r="E22" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F22" s="20">
         <v>45608</v>
       </c>
-      <c r="G18" s="21">
+      <c r="G22" s="21">
         <v>700</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="28"/>
-      <c r="B19" s="20">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="28"/>
+      <c r="B23" s="20">
         <v>45551</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C23" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="D23" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="E19" s="29" t="s">
+      <c r="E23" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="F19" s="20">
+      <c r="F23" s="20">
         <v>45611</v>
       </c>
-      <c r="G19" s="30">
+      <c r="G23" s="30">
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="28"/>
-      <c r="B20" s="20">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="28"/>
+      <c r="B24" s="20">
         <v>45558</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C24" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="D20" s="31" t="s">
+      <c r="D24" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="E20" s="29" t="s">
+      <c r="E24" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="F20" s="20">
+      <c r="F24" s="20">
         <v>45560</v>
       </c>
-      <c r="G20" s="30">
+      <c r="G24" s="30">
         <v>109</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="28"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="30"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="25"/>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="23">
-        <v>2023</v>
-      </c>
-      <c r="B23" s="9">
-        <v>44963</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="F23" s="9">
-        <v>45030</v>
-      </c>
-      <c r="G23" s="18" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="19"/>
-      <c r="B24" s="20">
-        <v>45139</v>
-      </c>
-      <c r="C24" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G24" s="21">
-        <v>93</v>
-      </c>
-    </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="19"/>
-      <c r="B25" s="20">
-        <v>45161</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="D25" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="E25" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="F25" s="20">
-        <v>45226</v>
-      </c>
-      <c r="G25" s="21">
-        <v>66</v>
-      </c>
+      <c r="A25" s="28"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="30"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="19"/>
-      <c r="B26" s="20">
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="25"/>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="23">
+        <v>2023</v>
+      </c>
+      <c r="B27" s="9">
+        <v>44963</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="F27" s="9">
+        <v>45030</v>
+      </c>
+      <c r="G27" s="18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="19"/>
+      <c r="B28" s="20">
+        <v>45139</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="21">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="19"/>
+      <c r="B29" s="20">
+        <v>45161</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" s="20">
+        <v>45226</v>
+      </c>
+      <c r="G29" s="21">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="19"/>
+      <c r="B30" s="20">
         <v>45174</v>
       </c>
-      <c r="C26" s="21" t="s">
+      <c r="C30" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="D26" s="21" t="s">
+      <c r="D30" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="E26" s="21" t="s">
+      <c r="E30" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="F26" s="20">
+      <c r="F30" s="20">
         <v>45231</v>
       </c>
-      <c r="G26" s="21" t="s">
+      <c r="G30" s="21" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="24">
+    <row r="31" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="24">
         <v>2021</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B31" s="5">
         <v>44438</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C31" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D31" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E31" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F31" s="5">
         <v>44530</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G31" s="6">
         <v>99</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="24">
+    <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="24">
         <v>2020</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B32" s="5">
         <v>43843</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C32" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D32" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E32" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F32" s="5">
         <v>43922</v>
       </c>
-      <c r="G28" s="6">
+      <c r="G32" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="6"/>
-      <c r="B29" s="5">
+    <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="6"/>
+      <c r="B33" s="5">
         <v>43871</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C33" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D33" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F33" s="5">
         <v>43946</v>
       </c>
-      <c r="G29" s="6">
+      <c r="G33" s="6">
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="6"/>
-      <c r="B30" s="5">
+    <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="6"/>
+      <c r="B34" s="5">
         <v>43914</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C34" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D34" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E34" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F34" s="5">
         <v>43915</v>
       </c>
-      <c r="G30" s="6">
+      <c r="G34" s="6">
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="6"/>
-      <c r="B31" s="5">
+    <row r="35" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="6"/>
+      <c r="B35" s="5">
         <v>43915</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C35" s="6" t="s">
         <v>42</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F31" s="5">
-        <v>43915</v>
-      </c>
-      <c r="G31" s="6">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="6"/>
-      <c r="B32" s="5">
-        <v>43915</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F32" s="5">
-        <v>43915</v>
-      </c>
-      <c r="G32" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="13"/>
-      <c r="B33" s="5">
-        <v>43916</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F33" s="5">
-        <v>43916</v>
-      </c>
-      <c r="G33" s="6">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="13"/>
-      <c r="B34" s="5">
-        <v>43924</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F34" s="5">
-        <v>43924</v>
-      </c>
-      <c r="G34" s="6">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="13"/>
-      <c r="B35" s="5">
-        <v>43924</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>50</v>
+        <v>36</v>
+      </c>
+      <c r="F35" s="5">
+        <v>43915</v>
       </c>
       <c r="G35" s="6">
-        <v>50</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="13"/>
+      <c r="A36" s="6"/>
       <c r="B36" s="5">
-        <v>43941</v>
+        <v>43915</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F36" s="5">
-        <v>43913</v>
+        <v>43915</v>
       </c>
       <c r="G36" s="6">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="13"/>
       <c r="B37" s="5">
-        <v>43941</v>
+        <v>43916</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F37" s="5">
-        <v>43913</v>
+        <v>43916</v>
       </c>
       <c r="G37" s="6">
-        <v>83</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="13"/>
       <c r="B38" s="5">
-        <v>43956</v>
+        <v>43924</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F38" s="5">
-        <v>44019</v>
+        <v>43924</v>
       </c>
       <c r="G38" s="6">
-        <v>79</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="13"/>
       <c r="B39" s="5">
-        <v>44174</v>
+        <v>43924</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F39" s="5">
-        <v>44167</v>
+        <v>51</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="G39" s="6">
-        <v>76</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="13"/>
       <c r="B40" s="5">
-        <v>44174</v>
+        <v>43941</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>38</v>
       </c>
       <c r="F40" s="5">
+        <v>43913</v>
+      </c>
+      <c r="G40" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="13"/>
+      <c r="B41" s="5">
+        <v>43941</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F41" s="5">
+        <v>43913</v>
+      </c>
+      <c r="G41" s="6">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="13"/>
+      <c r="B42" s="5">
+        <v>43956</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F42" s="5">
+        <v>44019</v>
+      </c>
+      <c r="G42" s="6">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="13"/>
+      <c r="B43" s="5">
+        <v>44174</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F43" s="5">
+        <v>44167</v>
+      </c>
+      <c r="G43" s="6">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="13"/>
+      <c r="B44" s="5">
+        <v>44174</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F44" s="5">
         <v>44228</v>
       </c>
-      <c r="G40" s="6">
+      <c r="G44" s="6">
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="24">
+    <row r="45" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="24">
         <v>2018</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B45" s="5">
         <v>43208</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C45" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D45" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F41" s="5">
+      <c r="F45" s="5">
         <v>43374</v>
       </c>
-      <c r="G41" s="6">
+      <c r="G45" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="33">
+    <row r="46" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="33">
         <v>2017</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B46" s="7">
         <v>42815</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="E46" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F42" s="7">
+      <c r="F46" s="7">
         <v>42916</v>
       </c>
-      <c r="G42" s="4">
+      <c r="G46" s="4">
         <v>80</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="33">
-        <v>2016</v>
-      </c>
-      <c r="B43" s="7">
-        <v>42373</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F43" s="7">
-        <v>42275</v>
-      </c>
-      <c r="G43" s="4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="14"/>
-      <c r="B44" s="7">
-        <v>42389</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F44" s="7">
-        <v>42460</v>
-      </c>
-      <c r="G44" s="4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="15"/>
-      <c r="B45" s="7">
-        <v>42459</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F45" s="7">
-        <v>42491</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="16"/>
-      <c r="B46" s="7">
-        <v>42543</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F46" s="7">
-        <v>42617</v>
-      </c>
-      <c r="G46" s="4">
-        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="33">
-        <v>2015</v>
-      </c>
-      <c r="B47" s="8">
-        <v>42033</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>29</v>
+        <v>2016</v>
+      </c>
+      <c r="B47" s="7">
+        <v>42373</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F47" s="11">
-        <v>42094</v>
-      </c>
-      <c r="G47" s="12">
-        <v>65</v>
+        <v>16</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47" s="7">
+        <v>42275</v>
+      </c>
+      <c r="G47" s="4">
+        <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="14"/>
-      <c r="B48" s="9">
-        <v>42131</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>30</v>
+      <c r="B48" s="7">
+        <v>42389</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F48" s="11">
-        <v>42369</v>
-      </c>
-      <c r="G48" s="12">
-        <v>341</v>
+        <v>21</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F48" s="7">
+        <v>42460</v>
+      </c>
+      <c r="G48" s="4">
+        <v>50</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="15"/>
-      <c r="B49" s="9">
-        <v>42270</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>31</v>
+      <c r="B49" s="7">
+        <v>42459</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F49" s="11">
-        <v>42338</v>
-      </c>
-      <c r="G49" s="12">
-        <v>140</v>
+        <v>24</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F49" s="7">
+        <v>42491</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="16"/>
-      <c r="B50" s="17">
+      <c r="B50" s="7">
+        <v>42543</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50" s="7">
+        <v>42617</v>
+      </c>
+      <c r="G50" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="33">
+        <v>2015</v>
+      </c>
+      <c r="B51" s="8">
+        <v>42033</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F51" s="11">
+        <v>42094</v>
+      </c>
+      <c r="G51" s="12">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="14"/>
+      <c r="B52" s="9">
+        <v>42131</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F52" s="11">
+        <v>42369</v>
+      </c>
+      <c r="G52" s="12">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="15"/>
+      <c r="B53" s="9">
+        <v>42270</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F53" s="11">
+        <v>42338</v>
+      </c>
+      <c r="G53" s="12">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="16"/>
+      <c r="B54" s="17">
         <v>42312</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C54" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="D54" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E54" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F50" s="11">
+      <c r="F54" s="11">
         <v>42355</v>
       </c>
-      <c r="G50" s="12" t="s">
+      <c r="G54" s="12" t="s">
         <v>40</v>
       </c>
     </row>
